--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247534</v>
+        <v>113247505</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>90045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536166</v>
+        <v>536194</v>
       </c>
       <c r="R2" t="n">
-        <v>7200537</v>
+        <v>7200560</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247562</v>
+        <v>113247520</v>
       </c>
       <c r="B3" t="n">
-        <v>78105</v>
+        <v>56765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536283</v>
+        <v>536030</v>
       </c>
       <c r="R3" t="n">
-        <v>7200533</v>
+        <v>7200575</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247506</v>
+        <v>113247503</v>
       </c>
       <c r="B4" t="n">
-        <v>90711</v>
+        <v>77116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536251</v>
+        <v>536467</v>
       </c>
       <c r="R4" t="n">
-        <v>7200583</v>
+        <v>7200485</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247566</v>
+        <v>113247543</v>
       </c>
       <c r="B5" t="n">
-        <v>78105</v>
+        <v>79184</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536254</v>
+        <v>536427</v>
       </c>
       <c r="R5" t="n">
-        <v>7200590</v>
+        <v>7200410</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247505</v>
+        <v>113247535</v>
       </c>
       <c r="B6" t="n">
-        <v>90029</v>
+        <v>79185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536194</v>
+        <v>536301</v>
       </c>
       <c r="R6" t="n">
-        <v>7200560</v>
+        <v>7200454</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247536</v>
+        <v>113247528</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>56910</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,34 +1256,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536284</v>
+        <v>536056</v>
       </c>
       <c r="R7" t="n">
-        <v>7200544</v>
+        <v>7200559</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247563</v>
+        <v>113247545</v>
       </c>
       <c r="B8" t="n">
-        <v>78105</v>
+        <v>77102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536283</v>
+        <v>536470</v>
       </c>
       <c r="R8" t="n">
-        <v>7200544</v>
+        <v>7200485</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247520</v>
+        <v>113247538</v>
       </c>
       <c r="B9" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1484,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536030</v>
+        <v>536129</v>
       </c>
       <c r="R9" t="n">
-        <v>7200575</v>
+        <v>7200562</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247535</v>
+        <v>113247564</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536301</v>
+        <v>536273</v>
       </c>
       <c r="R10" t="n">
-        <v>7200454</v>
+        <v>7200574</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247558</v>
+        <v>113247506</v>
       </c>
       <c r="B11" t="n">
-        <v>78105</v>
+        <v>90727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536183</v>
+        <v>536251</v>
       </c>
       <c r="R11" t="n">
-        <v>7200463</v>
+        <v>7200583</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247543</v>
+        <v>113247563</v>
       </c>
       <c r="B12" t="n">
-        <v>79168</v>
+        <v>78121</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536427</v>
+        <v>536283</v>
       </c>
       <c r="R12" t="n">
-        <v>7200410</v>
+        <v>7200544</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247567</v>
+        <v>113247537</v>
       </c>
       <c r="B13" t="n">
-        <v>78105</v>
+        <v>79185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536194</v>
+        <v>536163</v>
       </c>
       <c r="R13" t="n">
-        <v>7200560</v>
+        <v>7200558</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247564</v>
+        <v>113247542</v>
       </c>
       <c r="B14" t="n">
-        <v>78105</v>
+        <v>79184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536273</v>
+        <v>536166</v>
       </c>
       <c r="R14" t="n">
-        <v>7200574</v>
+        <v>7200538</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247559</v>
+        <v>113247561</v>
       </c>
       <c r="B15" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536304</v>
+        <v>536454</v>
       </c>
       <c r="R15" t="n">
-        <v>7200451</v>
+        <v>7200443</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247548</v>
+        <v>113247519</v>
       </c>
       <c r="B16" t="n">
-        <v>90047</v>
+        <v>56765</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,34 +2268,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536284</v>
+        <v>536274</v>
       </c>
       <c r="R16" t="n">
-        <v>7200530</v>
+        <v>7200574</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247560</v>
+        <v>113247559</v>
       </c>
       <c r="B17" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536312</v>
+        <v>536304</v>
       </c>
       <c r="R17" t="n">
-        <v>7200439</v>
+        <v>7200451</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2481,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247545</v>
+        <v>113247560</v>
       </c>
       <c r="B18" t="n">
-        <v>77086</v>
+        <v>78121</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2497,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536470</v>
+        <v>536312</v>
       </c>
       <c r="R18" t="n">
-        <v>7200485</v>
+        <v>7200439</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247504</v>
+        <v>113247558</v>
       </c>
       <c r="B19" t="n">
-        <v>74286</v>
+        <v>78121</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2609,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536454</v>
+        <v>536183</v>
       </c>
       <c r="R19" t="n">
-        <v>7200443</v>
+        <v>7200463</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247542</v>
+        <v>113247544</v>
       </c>
       <c r="B20" t="n">
-        <v>79168</v>
+        <v>79184</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536166</v>
+        <v>536161</v>
       </c>
       <c r="R20" t="n">
-        <v>7200538</v>
+        <v>7200560</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247503</v>
+        <v>113247504</v>
       </c>
       <c r="B21" t="n">
-        <v>77100</v>
+        <v>74302</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,21 +2833,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536467</v>
+        <v>536454</v>
       </c>
       <c r="R21" t="n">
-        <v>7200485</v>
+        <v>7200443</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247517</v>
+        <v>113247534</v>
       </c>
       <c r="B22" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,39 +2945,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536089</v>
+        <v>536166</v>
       </c>
       <c r="R22" t="n">
-        <v>7200498</v>
+        <v>7200537</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,7 +3041,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247519</v>
+        <v>113247517</v>
       </c>
       <c r="B23" t="n">
         <v>56765</v>
@@ -3073,7 +3077,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3082,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536274</v>
+        <v>536089</v>
       </c>
       <c r="R23" t="n">
-        <v>7200574</v>
+        <v>7200498</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247544</v>
+        <v>113247536</v>
       </c>
       <c r="B24" t="n">
-        <v>79168</v>
+        <v>79185</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,21 +3174,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536161</v>
+        <v>536284</v>
       </c>
       <c r="R24" t="n">
-        <v>7200560</v>
+        <v>7200544</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3229,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247528</v>
+        <v>113247567</v>
       </c>
       <c r="B25" t="n">
-        <v>56910</v>
+        <v>78121</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3282,38 +3286,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536056</v>
+        <v>536194</v>
       </c>
       <c r="R25" t="n">
-        <v>7200559</v>
+        <v>7200560</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247537</v>
+        <v>113247562</v>
       </c>
       <c r="B26" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3398,21 +3398,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536163</v>
+        <v>536283</v>
       </c>
       <c r="R26" t="n">
-        <v>7200558</v>
+        <v>7200533</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247538</v>
+        <v>113247566</v>
       </c>
       <c r="B27" t="n">
-        <v>79169</v>
+        <v>78121</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536129</v>
+        <v>536254</v>
       </c>
       <c r="R27" t="n">
-        <v>7200562</v>
+        <v>7200590</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247561</v>
+        <v>113247548</v>
       </c>
       <c r="B28" t="n">
-        <v>78105</v>
+        <v>90063</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536454</v>
+        <v>536284</v>
       </c>
       <c r="R28" t="n">
-        <v>7200443</v>
+        <v>7200530</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247505</v>
+        <v>113247503</v>
       </c>
       <c r="B2" t="n">
-        <v>90045</v>
+        <v>77116</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536194</v>
+        <v>536467</v>
       </c>
       <c r="R2" t="n">
-        <v>7200560</v>
+        <v>7200485</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247520</v>
+        <v>113247543</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>79184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536030</v>
+        <v>536427</v>
       </c>
       <c r="R3" t="n">
-        <v>7200575</v>
+        <v>7200410</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247503</v>
+        <v>113247535</v>
       </c>
       <c r="B4" t="n">
-        <v>77116</v>
+        <v>79185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536467</v>
+        <v>536301</v>
       </c>
       <c r="R4" t="n">
-        <v>7200485</v>
+        <v>7200454</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247543</v>
+        <v>113247528</v>
       </c>
       <c r="B5" t="n">
-        <v>79184</v>
+        <v>56910</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1027,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536427</v>
+        <v>536056</v>
       </c>
       <c r="R5" t="n">
-        <v>7200410</v>
+        <v>7200559</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247535</v>
+        <v>113247505</v>
       </c>
       <c r="B6" t="n">
-        <v>79185</v>
+        <v>90045</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536301</v>
+        <v>536194</v>
       </c>
       <c r="R6" t="n">
-        <v>7200454</v>
+        <v>7200560</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247528</v>
+        <v>113247520</v>
       </c>
       <c r="B7" t="n">
-        <v>56910</v>
+        <v>56765</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,26 +1255,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536056</v>
+        <v>536030</v>
       </c>
       <c r="R7" t="n">
-        <v>7200559</v>
+        <v>7200575</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247561</v>
+        <v>113247519</v>
       </c>
       <c r="B15" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,34 +2156,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536454</v>
+        <v>536274</v>
       </c>
       <c r="R15" t="n">
-        <v>7200443</v>
+        <v>7200574</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247519</v>
+        <v>113247561</v>
       </c>
       <c r="B16" t="n">
-        <v>56765</v>
+        <v>78121</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,39 +2273,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536274</v>
+        <v>536454</v>
       </c>
       <c r="R16" t="n">
-        <v>7200574</v>
+        <v>7200443</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247566</v>
+        <v>113247548</v>
       </c>
       <c r="B27" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536254</v>
+        <v>536284</v>
       </c>
       <c r="R27" t="n">
-        <v>7200590</v>
+        <v>7200530</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247548</v>
+        <v>113247566</v>
       </c>
       <c r="B28" t="n">
-        <v>90063</v>
+        <v>78121</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536284</v>
+        <v>536254</v>
       </c>
       <c r="R28" t="n">
-        <v>7200530</v>
+        <v>7200590</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247503</v>
+        <v>113247544</v>
       </c>
       <c r="B2" t="n">
-        <v>77116</v>
+        <v>79184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536467</v>
+        <v>536161</v>
       </c>
       <c r="R2" t="n">
-        <v>7200485</v>
+        <v>7200560</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247543</v>
+        <v>113247519</v>
       </c>
       <c r="B3" t="n">
-        <v>79184</v>
+        <v>56765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536427</v>
+        <v>536274</v>
       </c>
       <c r="R3" t="n">
-        <v>7200410</v>
+        <v>7200574</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247535</v>
+        <v>113247542</v>
       </c>
       <c r="B4" t="n">
-        <v>79185</v>
+        <v>79184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536301</v>
+        <v>536166</v>
       </c>
       <c r="R4" t="n">
-        <v>7200454</v>
+        <v>7200538</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247528</v>
+        <v>113247503</v>
       </c>
       <c r="B5" t="n">
-        <v>56910</v>
+        <v>77116</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536056</v>
+        <v>536467</v>
       </c>
       <c r="R5" t="n">
-        <v>7200559</v>
+        <v>7200485</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247505</v>
+        <v>113247517</v>
       </c>
       <c r="B6" t="n">
-        <v>90045</v>
+        <v>56765</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536194</v>
+        <v>536089</v>
       </c>
       <c r="R6" t="n">
-        <v>7200560</v>
+        <v>7200498</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247520</v>
+        <v>113247543</v>
       </c>
       <c r="B7" t="n">
-        <v>56765</v>
+        <v>79184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536030</v>
+        <v>536427</v>
       </c>
       <c r="R7" t="n">
-        <v>7200575</v>
+        <v>7200410</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247545</v>
+        <v>113247566</v>
       </c>
       <c r="B8" t="n">
-        <v>77102</v>
+        <v>78121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536470</v>
+        <v>536254</v>
       </c>
       <c r="R8" t="n">
-        <v>7200485</v>
+        <v>7200590</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247538</v>
+        <v>113247558</v>
       </c>
       <c r="B9" t="n">
-        <v>79185</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536129</v>
+        <v>536183</v>
       </c>
       <c r="R9" t="n">
-        <v>7200562</v>
+        <v>7200463</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247564</v>
+        <v>113247563</v>
       </c>
       <c r="B10" t="n">
         <v>78121</v>
@@ -1620,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536273</v>
+        <v>536283</v>
       </c>
       <c r="R10" t="n">
-        <v>7200574</v>
+        <v>7200544</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247506</v>
+        <v>113247560</v>
       </c>
       <c r="B11" t="n">
-        <v>90727</v>
+        <v>78121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536251</v>
+        <v>536312</v>
       </c>
       <c r="R11" t="n">
-        <v>7200583</v>
+        <v>7200439</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247563</v>
+        <v>113247548</v>
       </c>
       <c r="B12" t="n">
-        <v>78121</v>
+        <v>90063</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536283</v>
+        <v>536284</v>
       </c>
       <c r="R12" t="n">
-        <v>7200544</v>
+        <v>7200530</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247537</v>
+        <v>113247505</v>
       </c>
       <c r="B13" t="n">
-        <v>79185</v>
+        <v>90045</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536163</v>
+        <v>536194</v>
       </c>
       <c r="R13" t="n">
-        <v>7200558</v>
+        <v>7200560</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247542</v>
+        <v>113247506</v>
       </c>
       <c r="B14" t="n">
-        <v>79184</v>
+        <v>90727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2041,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536166</v>
+        <v>536251</v>
       </c>
       <c r="R14" t="n">
-        <v>7200538</v>
+        <v>7200583</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247519</v>
+        <v>113247545</v>
       </c>
       <c r="B15" t="n">
-        <v>56765</v>
+        <v>77102</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,39 +2157,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536274</v>
+        <v>536470</v>
       </c>
       <c r="R15" t="n">
-        <v>7200574</v>
+        <v>7200485</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247561</v>
+        <v>113247536</v>
       </c>
       <c r="B16" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2297,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536454</v>
+        <v>536284</v>
       </c>
       <c r="R16" t="n">
-        <v>7200443</v>
+        <v>7200544</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247559</v>
+        <v>113247535</v>
       </c>
       <c r="B17" t="n">
-        <v>78121</v>
+        <v>79185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536304</v>
+        <v>536301</v>
       </c>
       <c r="R17" t="n">
-        <v>7200451</v>
+        <v>7200454</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2481,7 +2477,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247560</v>
+        <v>113247567</v>
       </c>
       <c r="B18" t="n">
         <v>78121</v>
@@ -2521,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536312</v>
+        <v>536194</v>
       </c>
       <c r="R18" t="n">
-        <v>7200439</v>
+        <v>7200560</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2556,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2566,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247558</v>
+        <v>113247520</v>
       </c>
       <c r="B19" t="n">
-        <v>78121</v>
+        <v>56765</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,34 +2605,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536183</v>
+        <v>536030</v>
       </c>
       <c r="R19" t="n">
-        <v>7200463</v>
+        <v>7200575</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2669,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2679,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247544</v>
+        <v>113247528</v>
       </c>
       <c r="B20" t="n">
-        <v>79184</v>
+        <v>56910</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,34 +2722,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536161</v>
+        <v>536056</v>
       </c>
       <c r="R20" t="n">
-        <v>7200560</v>
+        <v>7200559</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2785,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2795,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247504</v>
+        <v>113247564</v>
       </c>
       <c r="B21" t="n">
-        <v>74302</v>
+        <v>78121</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2838,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536454</v>
+        <v>536273</v>
       </c>
       <c r="R21" t="n">
-        <v>7200443</v>
+        <v>7200574</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2897,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2907,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3041,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247517</v>
+        <v>113247537</v>
       </c>
       <c r="B23" t="n">
-        <v>56765</v>
+        <v>79185</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,39 +3062,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536089</v>
+        <v>536163</v>
       </c>
       <c r="R23" t="n">
-        <v>7200498</v>
+        <v>7200558</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,7 +3158,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247536</v>
+        <v>113247538</v>
       </c>
       <c r="B24" t="n">
         <v>79185</v>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536284</v>
+        <v>536129</v>
       </c>
       <c r="R24" t="n">
-        <v>7200544</v>
+        <v>7200562</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,7 +3270,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247567</v>
+        <v>113247562</v>
       </c>
       <c r="B25" t="n">
         <v>78121</v>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536194</v>
+        <v>536283</v>
       </c>
       <c r="R25" t="n">
-        <v>7200560</v>
+        <v>7200533</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,7 +3382,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247562</v>
+        <v>113247559</v>
       </c>
       <c r="B26" t="n">
         <v>78121</v>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536283</v>
+        <v>536304</v>
       </c>
       <c r="R26" t="n">
-        <v>7200533</v>
+        <v>7200451</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247548</v>
+        <v>113247504</v>
       </c>
       <c r="B27" t="n">
-        <v>90063</v>
+        <v>74302</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536284</v>
+        <v>536454</v>
       </c>
       <c r="R27" t="n">
-        <v>7200530</v>
+        <v>7200443</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,7 +3606,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247566</v>
+        <v>113247561</v>
       </c>
       <c r="B28" t="n">
         <v>78121</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536254</v>
+        <v>536454</v>
       </c>
       <c r="R28" t="n">
-        <v>7200590</v>
+        <v>7200443</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247544</v>
+        <v>113247506</v>
       </c>
       <c r="B2" t="n">
-        <v>79184</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536161</v>
+        <v>536251</v>
       </c>
       <c r="R2" t="n">
-        <v>7200560</v>
+        <v>7200583</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247519</v>
+        <v>113247561</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>78133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536274</v>
+        <v>536454</v>
       </c>
       <c r="R3" t="n">
-        <v>7200574</v>
+        <v>7200443</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +902,7 @@
         <v>113247542</v>
       </c>
       <c r="B4" t="n">
-        <v>79184</v>
+        <v>79196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247503</v>
+        <v>113247544</v>
       </c>
       <c r="B5" t="n">
-        <v>77116</v>
+        <v>79196</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536467</v>
+        <v>536161</v>
       </c>
       <c r="R5" t="n">
-        <v>7200485</v>
+        <v>7200560</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247517</v>
+        <v>113247534</v>
       </c>
       <c r="B6" t="n">
-        <v>56765</v>
+        <v>79197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536089</v>
+        <v>536166</v>
       </c>
       <c r="R6" t="n">
-        <v>7200498</v>
+        <v>7200537</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247543</v>
+        <v>113247528</v>
       </c>
       <c r="B7" t="n">
-        <v>79184</v>
+        <v>56911</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1251,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536427</v>
+        <v>536056</v>
       </c>
       <c r="R7" t="n">
-        <v>7200410</v>
+        <v>7200559</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247566</v>
+        <v>113247560</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536254</v>
+        <v>536312</v>
       </c>
       <c r="R8" t="n">
-        <v>7200590</v>
+        <v>7200439</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247558</v>
+        <v>113247519</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>56766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1479,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536183</v>
+        <v>536274</v>
       </c>
       <c r="R9" t="n">
-        <v>7200463</v>
+        <v>7200574</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247563</v>
+        <v>113247566</v>
       </c>
       <c r="B10" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536283</v>
+        <v>536254</v>
       </c>
       <c r="R10" t="n">
-        <v>7200544</v>
+        <v>7200590</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247560</v>
+        <v>113247564</v>
       </c>
       <c r="B11" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536312</v>
+        <v>536273</v>
       </c>
       <c r="R11" t="n">
-        <v>7200439</v>
+        <v>7200574</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247548</v>
+        <v>113247563</v>
       </c>
       <c r="B12" t="n">
-        <v>90063</v>
+        <v>78133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536284</v>
+        <v>536283</v>
       </c>
       <c r="R12" t="n">
-        <v>7200530</v>
+        <v>7200544</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,7 +1919,7 @@
         <v>113247505</v>
       </c>
       <c r="B13" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2029,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247506</v>
+        <v>113247543</v>
       </c>
       <c r="B14" t="n">
-        <v>90727</v>
+        <v>79196</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536251</v>
+        <v>536427</v>
       </c>
       <c r="R14" t="n">
-        <v>7200583</v>
+        <v>7200410</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247545</v>
+        <v>113247567</v>
       </c>
       <c r="B15" t="n">
-        <v>77102</v>
+        <v>78133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536470</v>
+        <v>536194</v>
       </c>
       <c r="R15" t="n">
-        <v>7200485</v>
+        <v>7200560</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247536</v>
+        <v>113247538</v>
       </c>
       <c r="B16" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536284</v>
+        <v>536129</v>
       </c>
       <c r="R16" t="n">
-        <v>7200544</v>
+        <v>7200562</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247535</v>
+        <v>113247503</v>
       </c>
       <c r="B17" t="n">
-        <v>79185</v>
+        <v>77128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,21 +2380,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536301</v>
+        <v>536467</v>
       </c>
       <c r="R17" t="n">
-        <v>7200454</v>
+        <v>7200485</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247567</v>
+        <v>113247559</v>
       </c>
       <c r="B18" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536194</v>
+        <v>536304</v>
       </c>
       <c r="R18" t="n">
-        <v>7200560</v>
+        <v>7200451</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247520</v>
+        <v>113247548</v>
       </c>
       <c r="B19" t="n">
-        <v>56765</v>
+        <v>90075</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,39 +2604,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536030</v>
+        <v>536284</v>
       </c>
       <c r="R19" t="n">
-        <v>7200575</v>
+        <v>7200530</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247528</v>
+        <v>113247517</v>
       </c>
       <c r="B20" t="n">
-        <v>56910</v>
+        <v>56766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,26 +2716,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2750,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536056</v>
+        <v>536089</v>
       </c>
       <c r="R20" t="n">
-        <v>7200559</v>
+        <v>7200498</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2785,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2795,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247564</v>
+        <v>113247535</v>
       </c>
       <c r="B21" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2838,21 +2833,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536273</v>
+        <v>536301</v>
       </c>
       <c r="R21" t="n">
-        <v>7200574</v>
+        <v>7200454</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2907,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247534</v>
+        <v>113247520</v>
       </c>
       <c r="B22" t="n">
-        <v>79185</v>
+        <v>56766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,34 +2945,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536166</v>
+        <v>536030</v>
       </c>
       <c r="R22" t="n">
-        <v>7200537</v>
+        <v>7200575</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3046,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247537</v>
+        <v>113247558</v>
       </c>
       <c r="B23" t="n">
-        <v>79185</v>
+        <v>78133</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536163</v>
+        <v>536183</v>
       </c>
       <c r="R23" t="n">
-        <v>7200558</v>
+        <v>7200463</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247538</v>
+        <v>113247504</v>
       </c>
       <c r="B24" t="n">
-        <v>79185</v>
+        <v>74314</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536129</v>
+        <v>536454</v>
       </c>
       <c r="R24" t="n">
-        <v>7200562</v>
+        <v>7200443</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247562</v>
+        <v>113247537</v>
       </c>
       <c r="B25" t="n">
-        <v>78121</v>
+        <v>79197</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536283</v>
+        <v>536163</v>
       </c>
       <c r="R25" t="n">
-        <v>7200533</v>
+        <v>7200558</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247559</v>
+        <v>113247562</v>
       </c>
       <c r="B26" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536304</v>
+        <v>536283</v>
       </c>
       <c r="R26" t="n">
-        <v>7200451</v>
+        <v>7200533</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247504</v>
+        <v>113247536</v>
       </c>
       <c r="B27" t="n">
-        <v>74302</v>
+        <v>79197</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536454</v>
+        <v>536284</v>
       </c>
       <c r="R27" t="n">
-        <v>7200443</v>
+        <v>7200544</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247561</v>
+        <v>113247545</v>
       </c>
       <c r="B28" t="n">
-        <v>78121</v>
+        <v>77114</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536454</v>
+        <v>536470</v>
       </c>
       <c r="R28" t="n">
-        <v>7200443</v>
+        <v>7200485</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247506</v>
+        <v>113247567</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536251</v>
+        <v>536194</v>
       </c>
       <c r="R2" t="n">
-        <v>7200583</v>
+        <v>7200560</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247561</v>
+        <v>113247560</v>
       </c>
       <c r="B3" t="n">
         <v>78133</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536454</v>
+        <v>536312</v>
       </c>
       <c r="R3" t="n">
-        <v>7200443</v>
+        <v>7200439</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247542</v>
+        <v>113247545</v>
       </c>
       <c r="B4" t="n">
-        <v>79196</v>
+        <v>77114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536166</v>
+        <v>536470</v>
       </c>
       <c r="R4" t="n">
-        <v>7200538</v>
+        <v>7200485</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247544</v>
+        <v>113247528</v>
       </c>
       <c r="B5" t="n">
-        <v>79196</v>
+        <v>56911</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536161</v>
+        <v>536056</v>
       </c>
       <c r="R5" t="n">
-        <v>7200560</v>
+        <v>7200559</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247528</v>
+        <v>113247559</v>
       </c>
       <c r="B7" t="n">
-        <v>56911</v>
+        <v>78133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,38 +1255,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536056</v>
+        <v>536304</v>
       </c>
       <c r="R7" t="n">
-        <v>7200559</v>
+        <v>7200451</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247560</v>
+        <v>113247503</v>
       </c>
       <c r="B8" t="n">
-        <v>78133</v>
+        <v>77128</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536312</v>
+        <v>536467</v>
       </c>
       <c r="R8" t="n">
-        <v>7200439</v>
+        <v>7200485</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247519</v>
+        <v>113247562</v>
       </c>
       <c r="B9" t="n">
-        <v>56766</v>
+        <v>78133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,39 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536274</v>
+        <v>536283</v>
       </c>
       <c r="R9" t="n">
-        <v>7200574</v>
+        <v>7200533</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247566</v>
+        <v>113247506</v>
       </c>
       <c r="B10" t="n">
-        <v>78133</v>
+        <v>90739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536254</v>
+        <v>536251</v>
       </c>
       <c r="R10" t="n">
-        <v>7200590</v>
+        <v>7200583</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1692,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247564</v>
+        <v>113247519</v>
       </c>
       <c r="B11" t="n">
-        <v>78133</v>
+        <v>56766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,31 +1703,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536273</v>
+        <v>536274</v>
       </c>
       <c r="R11" t="n">
         <v>7200574</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247505</v>
+        <v>113247543</v>
       </c>
       <c r="B13" t="n">
-        <v>90057</v>
+        <v>79196</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536194</v>
+        <v>536427</v>
       </c>
       <c r="R13" t="n">
-        <v>7200560</v>
+        <v>7200410</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247543</v>
+        <v>113247517</v>
       </c>
       <c r="B14" t="n">
-        <v>79196</v>
+        <v>56766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,34 +2044,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536427</v>
+        <v>536089</v>
       </c>
       <c r="R14" t="n">
-        <v>7200410</v>
+        <v>7200498</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247567</v>
+        <v>113247536</v>
       </c>
       <c r="B15" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,21 +2161,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536194</v>
+        <v>536284</v>
       </c>
       <c r="R15" t="n">
-        <v>7200560</v>
+        <v>7200544</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,7 +2257,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247538</v>
+        <v>113247535</v>
       </c>
       <c r="B16" t="n">
         <v>79197</v>
@@ -2292,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536129</v>
+        <v>536301</v>
       </c>
       <c r="R16" t="n">
-        <v>7200562</v>
+        <v>7200454</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247503</v>
+        <v>113247548</v>
       </c>
       <c r="B17" t="n">
-        <v>77128</v>
+        <v>90075</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,21 +2385,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536467</v>
+        <v>536284</v>
       </c>
       <c r="R17" t="n">
-        <v>7200485</v>
+        <v>7200530</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2481,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247559</v>
+        <v>113247542</v>
       </c>
       <c r="B18" t="n">
-        <v>78133</v>
+        <v>79196</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,21 +2497,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536304</v>
+        <v>536166</v>
       </c>
       <c r="R18" t="n">
-        <v>7200451</v>
+        <v>7200538</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247548</v>
+        <v>113247566</v>
       </c>
       <c r="B19" t="n">
-        <v>90075</v>
+        <v>78133</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,21 +2609,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536284</v>
+        <v>536254</v>
       </c>
       <c r="R19" t="n">
-        <v>7200530</v>
+        <v>7200590</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247517</v>
+        <v>113247537</v>
       </c>
       <c r="B20" t="n">
-        <v>56766</v>
+        <v>79197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,39 +2721,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536089</v>
+        <v>536163</v>
       </c>
       <c r="R20" t="n">
-        <v>7200498</v>
+        <v>7200558</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247535</v>
+        <v>113247538</v>
       </c>
       <c r="B21" t="n">
         <v>79197</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536301</v>
+        <v>536129</v>
       </c>
       <c r="R21" t="n">
-        <v>7200454</v>
+        <v>7200562</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3046,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247558</v>
+        <v>113247505</v>
       </c>
       <c r="B23" t="n">
-        <v>78133</v>
+        <v>90057</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536183</v>
+        <v>536194</v>
       </c>
       <c r="R23" t="n">
-        <v>7200463</v>
+        <v>7200560</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247504</v>
+        <v>113247564</v>
       </c>
       <c r="B24" t="n">
-        <v>74314</v>
+        <v>78133</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,21 +3174,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536454</v>
+        <v>536273</v>
       </c>
       <c r="R24" t="n">
-        <v>7200443</v>
+        <v>7200574</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247537</v>
+        <v>113247504</v>
       </c>
       <c r="B25" t="n">
-        <v>79197</v>
+        <v>74314</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536163</v>
+        <v>536454</v>
       </c>
       <c r="R25" t="n">
-        <v>7200558</v>
+        <v>7200443</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,7 +3382,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247562</v>
+        <v>113247561</v>
       </c>
       <c r="B26" t="n">
         <v>78133</v>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536283</v>
+        <v>536454</v>
       </c>
       <c r="R26" t="n">
-        <v>7200533</v>
+        <v>7200443</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247536</v>
+        <v>113247544</v>
       </c>
       <c r="B27" t="n">
-        <v>79197</v>
+        <v>79196</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536284</v>
+        <v>536161</v>
       </c>
       <c r="R27" t="n">
-        <v>7200544</v>
+        <v>7200560</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247545</v>
+        <v>113247558</v>
       </c>
       <c r="B28" t="n">
-        <v>77114</v>
+        <v>78133</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536470</v>
+        <v>536183</v>
       </c>
       <c r="R28" t="n">
-        <v>7200485</v>
+        <v>7200463</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247560</v>
+        <v>113247528</v>
       </c>
       <c r="B3" t="n">
-        <v>78133</v>
+        <v>56911</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536312</v>
+        <v>536056</v>
       </c>
       <c r="R3" t="n">
-        <v>7200439</v>
+        <v>7200559</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247528</v>
+        <v>113247560</v>
       </c>
       <c r="B5" t="n">
-        <v>56911</v>
+        <v>78133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536056</v>
+        <v>536312</v>
       </c>
       <c r="R5" t="n">
-        <v>7200559</v>
+        <v>7200439</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247543</v>
+        <v>113247536</v>
       </c>
       <c r="B13" t="n">
-        <v>79196</v>
+        <v>79197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536427</v>
+        <v>536284</v>
       </c>
       <c r="R13" t="n">
-        <v>7200410</v>
+        <v>7200544</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247517</v>
+        <v>113247535</v>
       </c>
       <c r="B14" t="n">
-        <v>56766</v>
+        <v>79197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,39 +2044,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536089</v>
+        <v>536301</v>
       </c>
       <c r="R14" t="n">
-        <v>7200498</v>
+        <v>7200454</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247536</v>
+        <v>113247548</v>
       </c>
       <c r="B15" t="n">
-        <v>79197</v>
+        <v>90075</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2188,7 +2183,7 @@
         <v>536284</v>
       </c>
       <c r="R15" t="n">
-        <v>7200544</v>
+        <v>7200530</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247535</v>
+        <v>113247543</v>
       </c>
       <c r="B16" t="n">
-        <v>79197</v>
+        <v>79196</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,21 +2268,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536301</v>
+        <v>536427</v>
       </c>
       <c r="R16" t="n">
-        <v>7200454</v>
+        <v>7200410</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247548</v>
+        <v>113247517</v>
       </c>
       <c r="B17" t="n">
-        <v>90075</v>
+        <v>56766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,34 +2380,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536284</v>
+        <v>536089</v>
       </c>
       <c r="R17" t="n">
-        <v>7200530</v>
+        <v>7200498</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247566</v>
+        <v>113247537</v>
       </c>
       <c r="B19" t="n">
-        <v>78133</v>
+        <v>79197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,21 +2609,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536254</v>
+        <v>536163</v>
       </c>
       <c r="R19" t="n">
-        <v>7200590</v>
+        <v>7200558</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247537</v>
+        <v>113247566</v>
       </c>
       <c r="B20" t="n">
-        <v>79197</v>
+        <v>78133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536163</v>
+        <v>536254</v>
       </c>
       <c r="R20" t="n">
-        <v>7200558</v>
+        <v>7200590</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247538</v>
+        <v>113247520</v>
       </c>
       <c r="B21" t="n">
-        <v>79197</v>
+        <v>56766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,34 +2833,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536129</v>
+        <v>536030</v>
       </c>
       <c r="R21" t="n">
-        <v>7200562</v>
+        <v>7200575</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2897,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2907,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247520</v>
+        <v>113247538</v>
       </c>
       <c r="B22" t="n">
-        <v>56766</v>
+        <v>79197</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,39 +2950,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536030</v>
+        <v>536129</v>
       </c>
       <c r="R22" t="n">
-        <v>7200575</v>
+        <v>7200562</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247567</v>
+        <v>113247562</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536194</v>
+        <v>536283</v>
       </c>
       <c r="R2" t="n">
-        <v>7200560</v>
+        <v>7200533</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247528</v>
+        <v>113247503</v>
       </c>
       <c r="B3" t="n">
-        <v>56911</v>
+        <v>77150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536056</v>
+        <v>536467</v>
       </c>
       <c r="R3" t="n">
-        <v>7200559</v>
+        <v>7200485</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247545</v>
+        <v>113247519</v>
       </c>
       <c r="B4" t="n">
-        <v>77114</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536470</v>
+        <v>536274</v>
       </c>
       <c r="R4" t="n">
-        <v>7200485</v>
+        <v>7200574</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247560</v>
+        <v>113247535</v>
       </c>
       <c r="B5" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536312</v>
+        <v>536301</v>
       </c>
       <c r="R5" t="n">
-        <v>7200439</v>
+        <v>7200454</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247534</v>
+        <v>113247548</v>
       </c>
       <c r="B6" t="n">
-        <v>79197</v>
+        <v>90097</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536166</v>
+        <v>536284</v>
       </c>
       <c r="R6" t="n">
-        <v>7200537</v>
+        <v>7200530</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247559</v>
+        <v>113247564</v>
       </c>
       <c r="B7" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536304</v>
+        <v>536273</v>
       </c>
       <c r="R7" t="n">
-        <v>7200451</v>
+        <v>7200574</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247503</v>
+        <v>113247560</v>
       </c>
       <c r="B8" t="n">
-        <v>77128</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536467</v>
+        <v>536312</v>
       </c>
       <c r="R8" t="n">
-        <v>7200485</v>
+        <v>7200439</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247562</v>
+        <v>113247538</v>
       </c>
       <c r="B9" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536283</v>
+        <v>536129</v>
       </c>
       <c r="R9" t="n">
-        <v>7200533</v>
+        <v>7200562</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247506</v>
+        <v>113247536</v>
       </c>
       <c r="B10" t="n">
-        <v>90739</v>
+        <v>79219</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536251</v>
+        <v>536284</v>
       </c>
       <c r="R10" t="n">
-        <v>7200583</v>
+        <v>7200544</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247519</v>
+        <v>113247566</v>
       </c>
       <c r="B11" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,39 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536274</v>
+        <v>536254</v>
       </c>
       <c r="R11" t="n">
-        <v>7200574</v>
+        <v>7200590</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247563</v>
+        <v>113247543</v>
       </c>
       <c r="B12" t="n">
-        <v>78133</v>
+        <v>79218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536283</v>
+        <v>536427</v>
       </c>
       <c r="R12" t="n">
-        <v>7200544</v>
+        <v>7200410</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247536</v>
+        <v>113247537</v>
       </c>
       <c r="B13" t="n">
-        <v>79197</v>
+        <v>79219</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536284</v>
+        <v>536163</v>
       </c>
       <c r="R13" t="n">
-        <v>7200544</v>
+        <v>7200558</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247535</v>
+        <v>113247520</v>
       </c>
       <c r="B14" t="n">
-        <v>79197</v>
+        <v>56766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,34 +2040,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536301</v>
+        <v>536030</v>
       </c>
       <c r="R14" t="n">
-        <v>7200454</v>
+        <v>7200575</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247548</v>
+        <v>113247506</v>
       </c>
       <c r="B15" t="n">
-        <v>90075</v>
+        <v>90761</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2153,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536284</v>
+        <v>536251</v>
       </c>
       <c r="R15" t="n">
-        <v>7200530</v>
+        <v>7200583</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247543</v>
+        <v>113247528</v>
       </c>
       <c r="B16" t="n">
-        <v>79196</v>
+        <v>56911</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,34 +2269,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536427</v>
+        <v>536056</v>
       </c>
       <c r="R16" t="n">
-        <v>7200410</v>
+        <v>7200559</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247517</v>
+        <v>113247563</v>
       </c>
       <c r="B17" t="n">
-        <v>56766</v>
+        <v>78155</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,39 +2385,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536089</v>
+        <v>536283</v>
       </c>
       <c r="R17" t="n">
-        <v>7200498</v>
+        <v>7200544</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247542</v>
+        <v>113247544</v>
       </c>
       <c r="B18" t="n">
-        <v>79196</v>
+        <v>79218</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536166</v>
+        <v>536161</v>
       </c>
       <c r="R18" t="n">
-        <v>7200538</v>
+        <v>7200560</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247537</v>
+        <v>113247559</v>
       </c>
       <c r="B19" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,21 +2609,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536163</v>
+        <v>536304</v>
       </c>
       <c r="R19" t="n">
-        <v>7200558</v>
+        <v>7200451</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247566</v>
+        <v>113247534</v>
       </c>
       <c r="B20" t="n">
-        <v>78133</v>
+        <v>79219</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536254</v>
+        <v>536166</v>
       </c>
       <c r="R20" t="n">
-        <v>7200590</v>
+        <v>7200537</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247520</v>
+        <v>113247542</v>
       </c>
       <c r="B21" t="n">
-        <v>56766</v>
+        <v>79218</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,39 +2833,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536030</v>
+        <v>536166</v>
       </c>
       <c r="R21" t="n">
-        <v>7200575</v>
+        <v>7200538</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2907,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247538</v>
+        <v>113247558</v>
       </c>
       <c r="B22" t="n">
-        <v>79197</v>
+        <v>78155</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2950,21 +2945,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2974,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536129</v>
+        <v>536183</v>
       </c>
       <c r="R22" t="n">
-        <v>7200562</v>
+        <v>7200463</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3009,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3019,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3046,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247505</v>
+        <v>113247504</v>
       </c>
       <c r="B23" t="n">
-        <v>90057</v>
+        <v>74336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3062,21 +3057,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536194</v>
+        <v>536454</v>
       </c>
       <c r="R23" t="n">
-        <v>7200560</v>
+        <v>7200443</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3121,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247564</v>
+        <v>113247505</v>
       </c>
       <c r="B24" t="n">
-        <v>78133</v>
+        <v>90079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3174,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536273</v>
+        <v>536194</v>
       </c>
       <c r="R24" t="n">
-        <v>7200574</v>
+        <v>7200560</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247504</v>
+        <v>113247517</v>
       </c>
       <c r="B25" t="n">
-        <v>74314</v>
+        <v>56766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,34 +3281,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536454</v>
+        <v>536089</v>
       </c>
       <c r="R25" t="n">
-        <v>7200443</v>
+        <v>7200498</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247561</v>
+        <v>113247567</v>
       </c>
       <c r="B26" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536454</v>
+        <v>536194</v>
       </c>
       <c r="R26" t="n">
-        <v>7200443</v>
+        <v>7200560</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247544</v>
+        <v>113247561</v>
       </c>
       <c r="B27" t="n">
-        <v>79196</v>
+        <v>78155</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536161</v>
+        <v>536454</v>
       </c>
       <c r="R27" t="n">
-        <v>7200560</v>
+        <v>7200443</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247558</v>
+        <v>113247545</v>
       </c>
       <c r="B28" t="n">
-        <v>78133</v>
+        <v>77136</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536183</v>
+        <v>536470</v>
       </c>
       <c r="R28" t="n">
-        <v>7200463</v>
+        <v>7200485</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113247562</v>
       </c>
       <c r="B2" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247503</v>
+        <v>113247506</v>
       </c>
       <c r="B3" t="n">
-        <v>77150</v>
+        <v>90765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536467</v>
+        <v>536251</v>
       </c>
       <c r="R3" t="n">
-        <v>7200485</v>
+        <v>7200583</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247519</v>
+        <v>113247543</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536274</v>
+        <v>536427</v>
       </c>
       <c r="R4" t="n">
-        <v>7200574</v>
+        <v>7200410</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247535</v>
+        <v>113247536</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536301</v>
+        <v>536284</v>
       </c>
       <c r="R5" t="n">
-        <v>7200454</v>
+        <v>7200544</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247548</v>
+        <v>113247503</v>
       </c>
       <c r="B6" t="n">
-        <v>90097</v>
+        <v>77153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536284</v>
+        <v>536467</v>
       </c>
       <c r="R6" t="n">
-        <v>7200530</v>
+        <v>7200485</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247564</v>
+        <v>113247560</v>
       </c>
       <c r="B7" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536273</v>
+        <v>536312</v>
       </c>
       <c r="R7" t="n">
-        <v>7200574</v>
+        <v>7200439</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247560</v>
+        <v>113247535</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536312</v>
+        <v>536301</v>
       </c>
       <c r="R8" t="n">
-        <v>7200439</v>
+        <v>7200454</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247538</v>
+        <v>113247520</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>56769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,34 +1475,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536129</v>
+        <v>536030</v>
       </c>
       <c r="R9" t="n">
-        <v>7200562</v>
+        <v>7200575</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247536</v>
+        <v>113247558</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>78158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536284</v>
+        <v>536183</v>
       </c>
       <c r="R10" t="n">
-        <v>7200544</v>
+        <v>7200463</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247566</v>
+        <v>113247505</v>
       </c>
       <c r="B11" t="n">
-        <v>78155</v>
+        <v>90083</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536254</v>
+        <v>536194</v>
       </c>
       <c r="R11" t="n">
-        <v>7200590</v>
+        <v>7200560</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247543</v>
+        <v>113247567</v>
       </c>
       <c r="B12" t="n">
-        <v>79218</v>
+        <v>78158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536427</v>
+        <v>536194</v>
       </c>
       <c r="R12" t="n">
-        <v>7200410</v>
+        <v>7200560</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247537</v>
+        <v>113247504</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>74339</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536163</v>
+        <v>536454</v>
       </c>
       <c r="R13" t="n">
-        <v>7200558</v>
+        <v>7200443</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247520</v>
+        <v>113247519</v>
       </c>
       <c r="B14" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536030</v>
+        <v>536274</v>
       </c>
       <c r="R14" t="n">
-        <v>7200575</v>
+        <v>7200574</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247506</v>
+        <v>113247545</v>
       </c>
       <c r="B15" t="n">
-        <v>90761</v>
+        <v>77139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,25 +2153,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536251</v>
+        <v>536470</v>
       </c>
       <c r="R15" t="n">
-        <v>7200583</v>
+        <v>7200485</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247528</v>
+        <v>113247561</v>
       </c>
       <c r="B16" t="n">
-        <v>56911</v>
+        <v>78158</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,38 +2269,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536056</v>
+        <v>536454</v>
       </c>
       <c r="R16" t="n">
-        <v>7200559</v>
+        <v>7200443</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,7 +2368,7 @@
         <v>113247563</v>
       </c>
       <c r="B17" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247544</v>
+        <v>113247537</v>
       </c>
       <c r="B18" t="n">
-        <v>79218</v>
+        <v>79223</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2497,21 +2493,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2521,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536161</v>
+        <v>536163</v>
       </c>
       <c r="R18" t="n">
-        <v>7200560</v>
+        <v>7200558</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2593,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247559</v>
+        <v>113247564</v>
       </c>
       <c r="B19" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536304</v>
+        <v>536273</v>
       </c>
       <c r="R19" t="n">
-        <v>7200451</v>
+        <v>7200574</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247534</v>
+        <v>113247528</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>56914</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,34 +2717,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536166</v>
+        <v>536056</v>
       </c>
       <c r="R20" t="n">
-        <v>7200537</v>
+        <v>7200559</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247542</v>
+        <v>113247538</v>
       </c>
       <c r="B21" t="n">
-        <v>79218</v>
+        <v>79223</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536166</v>
+        <v>536129</v>
       </c>
       <c r="R21" t="n">
-        <v>7200538</v>
+        <v>7200562</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247558</v>
+        <v>113247534</v>
       </c>
       <c r="B22" t="n">
-        <v>78155</v>
+        <v>79223</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536183</v>
+        <v>536166</v>
       </c>
       <c r="R22" t="n">
-        <v>7200463</v>
+        <v>7200537</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247504</v>
+        <v>113247566</v>
       </c>
       <c r="B23" t="n">
-        <v>74336</v>
+        <v>78158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,21 +3057,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536454</v>
+        <v>536254</v>
       </c>
       <c r="R23" t="n">
-        <v>7200443</v>
+        <v>7200590</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247505</v>
+        <v>113247517</v>
       </c>
       <c r="B24" t="n">
-        <v>90079</v>
+        <v>56769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,34 +3169,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536194</v>
+        <v>536089</v>
       </c>
       <c r="R24" t="n">
-        <v>7200560</v>
+        <v>7200498</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247517</v>
+        <v>113247542</v>
       </c>
       <c r="B25" t="n">
-        <v>56766</v>
+        <v>79222</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,39 +3286,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536089</v>
+        <v>536166</v>
       </c>
       <c r="R25" t="n">
-        <v>7200498</v>
+        <v>7200538</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247567</v>
+        <v>113247559</v>
       </c>
       <c r="B26" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536194</v>
+        <v>536304</v>
       </c>
       <c r="R26" t="n">
-        <v>7200560</v>
+        <v>7200451</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247561</v>
+        <v>113247548</v>
       </c>
       <c r="B27" t="n">
-        <v>78155</v>
+        <v>90101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536454</v>
+        <v>536284</v>
       </c>
       <c r="R27" t="n">
-        <v>7200443</v>
+        <v>7200530</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247545</v>
+        <v>113247544</v>
       </c>
       <c r="B28" t="n">
-        <v>77136</v>
+        <v>79222</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536470</v>
+        <v>536161</v>
       </c>
       <c r="R28" t="n">
-        <v>7200485</v>
+        <v>7200560</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247536</v>
+        <v>113247503</v>
       </c>
       <c r="B5" t="n">
-        <v>79223</v>
+        <v>77153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536284</v>
+        <v>536467</v>
       </c>
       <c r="R5" t="n">
-        <v>7200544</v>
+        <v>7200485</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247503</v>
+        <v>113247536</v>
       </c>
       <c r="B6" t="n">
-        <v>77153</v>
+        <v>79223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536467</v>
+        <v>536284</v>
       </c>
       <c r="R6" t="n">
-        <v>7200485</v>
+        <v>7200544</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247567</v>
+        <v>113247504</v>
       </c>
       <c r="B12" t="n">
-        <v>78158</v>
+        <v>74339</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536194</v>
+        <v>536454</v>
       </c>
       <c r="R12" t="n">
-        <v>7200560</v>
+        <v>7200443</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247504</v>
+        <v>113247519</v>
       </c>
       <c r="B13" t="n">
-        <v>74339</v>
+        <v>56769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,34 +1928,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536454</v>
+        <v>536274</v>
       </c>
       <c r="R13" t="n">
-        <v>7200443</v>
+        <v>7200574</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247519</v>
+        <v>113247567</v>
       </c>
       <c r="B14" t="n">
-        <v>56769</v>
+        <v>78158</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,39 +2045,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536274</v>
+        <v>536194</v>
       </c>
       <c r="R14" t="n">
-        <v>7200574</v>
+        <v>7200560</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247545</v>
+        <v>113247561</v>
       </c>
       <c r="B15" t="n">
-        <v>77139</v>
+        <v>78158</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2157,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536470</v>
+        <v>536454</v>
       </c>
       <c r="R15" t="n">
-        <v>7200485</v>
+        <v>7200443</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,7 +2253,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247561</v>
+        <v>113247563</v>
       </c>
       <c r="B16" t="n">
         <v>78158</v>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536454</v>
+        <v>536283</v>
       </c>
       <c r="R16" t="n">
-        <v>7200443</v>
+        <v>7200544</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247563</v>
+        <v>113247537</v>
       </c>
       <c r="B17" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536283</v>
+        <v>536163</v>
       </c>
       <c r="R17" t="n">
-        <v>7200544</v>
+        <v>7200558</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247537</v>
+        <v>113247545</v>
       </c>
       <c r="B18" t="n">
-        <v>79223</v>
+        <v>77139</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536163</v>
+        <v>536470</v>
       </c>
       <c r="R18" t="n">
-        <v>7200558</v>
+        <v>7200485</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247548</v>
+        <v>113247544</v>
       </c>
       <c r="B27" t="n">
-        <v>90101</v>
+        <v>79222</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536284</v>
+        <v>536161</v>
       </c>
       <c r="R27" t="n">
-        <v>7200530</v>
+        <v>7200560</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247544</v>
+        <v>113247548</v>
       </c>
       <c r="B28" t="n">
-        <v>79222</v>
+        <v>90101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536161</v>
+        <v>536284</v>
       </c>
       <c r="R28" t="n">
-        <v>7200560</v>
+        <v>7200530</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247562</v>
+        <v>113247545</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>77139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536283</v>
+        <v>536470</v>
       </c>
       <c r="R2" t="n">
-        <v>7200533</v>
+        <v>7200485</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247506</v>
+        <v>113247543</v>
       </c>
       <c r="B3" t="n">
-        <v>90765</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536251</v>
+        <v>536427</v>
       </c>
       <c r="R3" t="n">
-        <v>7200583</v>
+        <v>7200410</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247543</v>
+        <v>113247561</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>78158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536427</v>
+        <v>536454</v>
       </c>
       <c r="R4" t="n">
-        <v>7200410</v>
+        <v>7200443</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247503</v>
+        <v>113247567</v>
       </c>
       <c r="B5" t="n">
-        <v>77153</v>
+        <v>78158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536467</v>
+        <v>536194</v>
       </c>
       <c r="R5" t="n">
-        <v>7200485</v>
+        <v>7200560</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247536</v>
+        <v>113247560</v>
       </c>
       <c r="B6" t="n">
-        <v>79223</v>
+        <v>78158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536284</v>
+        <v>536312</v>
       </c>
       <c r="R6" t="n">
-        <v>7200544</v>
+        <v>7200439</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247560</v>
+        <v>113247559</v>
       </c>
       <c r="B7" t="n">
         <v>78158</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536312</v>
+        <v>536304</v>
       </c>
       <c r="R7" t="n">
-        <v>7200439</v>
+        <v>7200451</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247535</v>
+        <v>113247505</v>
       </c>
       <c r="B8" t="n">
-        <v>79223</v>
+        <v>90083</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536301</v>
+        <v>536194</v>
       </c>
       <c r="R8" t="n">
-        <v>7200454</v>
+        <v>7200560</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247520</v>
+        <v>113247534</v>
       </c>
       <c r="B9" t="n">
-        <v>56769</v>
+        <v>79223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536030</v>
+        <v>536166</v>
       </c>
       <c r="R9" t="n">
-        <v>7200575</v>
+        <v>7200537</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247558</v>
+        <v>113247544</v>
       </c>
       <c r="B10" t="n">
-        <v>78158</v>
+        <v>79222</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536183</v>
+        <v>536161</v>
       </c>
       <c r="R10" t="n">
-        <v>7200463</v>
+        <v>7200560</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247505</v>
+        <v>113247566</v>
       </c>
       <c r="B11" t="n">
-        <v>90083</v>
+        <v>78158</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536194</v>
+        <v>536254</v>
       </c>
       <c r="R11" t="n">
-        <v>7200560</v>
+        <v>7200590</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247504</v>
+        <v>113247506</v>
       </c>
       <c r="B12" t="n">
-        <v>74339</v>
+        <v>90765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536454</v>
+        <v>536251</v>
       </c>
       <c r="R12" t="n">
-        <v>7200443</v>
+        <v>7200583</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247519</v>
+        <v>113247548</v>
       </c>
       <c r="B13" t="n">
-        <v>56769</v>
+        <v>90101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,39 +1923,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536274</v>
+        <v>536284</v>
       </c>
       <c r="R13" t="n">
-        <v>7200574</v>
+        <v>7200530</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247567</v>
+        <v>113247562</v>
       </c>
       <c r="B14" t="n">
         <v>78158</v>
@@ -2069,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536194</v>
+        <v>536283</v>
       </c>
       <c r="R14" t="n">
-        <v>7200560</v>
+        <v>7200533</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247561</v>
+        <v>113247536</v>
       </c>
       <c r="B15" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536454</v>
+        <v>536284</v>
       </c>
       <c r="R15" t="n">
-        <v>7200443</v>
+        <v>7200544</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247563</v>
+        <v>113247537</v>
       </c>
       <c r="B16" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536283</v>
+        <v>536163</v>
       </c>
       <c r="R16" t="n">
-        <v>7200544</v>
+        <v>7200558</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247537</v>
+        <v>113247504</v>
       </c>
       <c r="B17" t="n">
-        <v>79223</v>
+        <v>74339</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536163</v>
+        <v>536454</v>
       </c>
       <c r="R17" t="n">
-        <v>7200558</v>
+        <v>7200443</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247545</v>
+        <v>113247528</v>
       </c>
       <c r="B18" t="n">
-        <v>77139</v>
+        <v>56914</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,34 +2483,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536470</v>
+        <v>536056</v>
       </c>
       <c r="R18" t="n">
-        <v>7200485</v>
+        <v>7200559</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247564</v>
+        <v>113247535</v>
       </c>
       <c r="B19" t="n">
-        <v>78158</v>
+        <v>79223</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536273</v>
+        <v>536301</v>
       </c>
       <c r="R19" t="n">
-        <v>7200574</v>
+        <v>7200454</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247528</v>
+        <v>113247538</v>
       </c>
       <c r="B20" t="n">
-        <v>56914</v>
+        <v>79223</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,38 +2711,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536056</v>
+        <v>536129</v>
       </c>
       <c r="R20" t="n">
-        <v>7200559</v>
+        <v>7200562</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247538</v>
+        <v>113247542</v>
       </c>
       <c r="B21" t="n">
-        <v>79223</v>
+        <v>79222</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2823,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536129</v>
+        <v>536166</v>
       </c>
       <c r="R21" t="n">
-        <v>7200562</v>
+        <v>7200538</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247534</v>
+        <v>113247517</v>
       </c>
       <c r="B22" t="n">
-        <v>79223</v>
+        <v>56769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,34 +2935,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536166</v>
+        <v>536089</v>
       </c>
       <c r="R22" t="n">
-        <v>7200537</v>
+        <v>7200498</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247566</v>
+        <v>113247520</v>
       </c>
       <c r="B23" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,34 +3052,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536254</v>
+        <v>536030</v>
       </c>
       <c r="R23" t="n">
-        <v>7200590</v>
+        <v>7200575</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247517</v>
+        <v>113247563</v>
       </c>
       <c r="B24" t="n">
-        <v>56769</v>
+        <v>78158</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,39 +3169,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536089</v>
+        <v>536283</v>
       </c>
       <c r="R24" t="n">
-        <v>7200498</v>
+        <v>7200544</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247542</v>
+        <v>113247503</v>
       </c>
       <c r="B25" t="n">
-        <v>79222</v>
+        <v>77153</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,21 +3281,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3310,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536166</v>
+        <v>536467</v>
       </c>
       <c r="R25" t="n">
-        <v>7200538</v>
+        <v>7200485</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247559</v>
+        <v>113247519</v>
       </c>
       <c r="B26" t="n">
-        <v>78158</v>
+        <v>56769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3398,34 +3393,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536304</v>
+        <v>536274</v>
       </c>
       <c r="R26" t="n">
-        <v>7200451</v>
+        <v>7200574</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247544</v>
+        <v>113247558</v>
       </c>
       <c r="B27" t="n">
-        <v>79222</v>
+        <v>78158</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536161</v>
+        <v>536183</v>
       </c>
       <c r="R27" t="n">
-        <v>7200560</v>
+        <v>7200463</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247548</v>
+        <v>113247564</v>
       </c>
       <c r="B28" t="n">
-        <v>90101</v>
+        <v>78158</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536284</v>
+        <v>536273</v>
       </c>
       <c r="R28" t="n">
-        <v>7200530</v>
+        <v>7200574</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247545</v>
+        <v>113247566</v>
       </c>
       <c r="B2" t="n">
-        <v>77139</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536470</v>
+        <v>536254</v>
       </c>
       <c r="R2" t="n">
-        <v>7200485</v>
+        <v>7200590</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247543</v>
+        <v>113247528</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>56918</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536427</v>
+        <v>536056</v>
       </c>
       <c r="R3" t="n">
-        <v>7200410</v>
+        <v>7200559</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247561</v>
+        <v>113247535</v>
       </c>
       <c r="B4" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536454</v>
+        <v>536301</v>
       </c>
       <c r="R4" t="n">
-        <v>7200443</v>
+        <v>7200454</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247567</v>
+        <v>113247559</v>
       </c>
       <c r="B5" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536194</v>
+        <v>536304</v>
       </c>
       <c r="R5" t="n">
-        <v>7200560</v>
+        <v>7200451</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247560</v>
+        <v>113247562</v>
       </c>
       <c r="B6" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536312</v>
+        <v>536283</v>
       </c>
       <c r="R6" t="n">
-        <v>7200439</v>
+        <v>7200533</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247559</v>
+        <v>113247536</v>
       </c>
       <c r="B7" t="n">
-        <v>78158</v>
+        <v>79229</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536304</v>
+        <v>536284</v>
       </c>
       <c r="R7" t="n">
-        <v>7200451</v>
+        <v>7200544</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247505</v>
+        <v>113247504</v>
       </c>
       <c r="B8" t="n">
-        <v>90083</v>
+        <v>74345</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536194</v>
+        <v>536454</v>
       </c>
       <c r="R8" t="n">
-        <v>7200560</v>
+        <v>7200443</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247534</v>
+        <v>113247537</v>
       </c>
       <c r="B9" t="n">
-        <v>79223</v>
+        <v>79229</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536166</v>
+        <v>536163</v>
       </c>
       <c r="R9" t="n">
-        <v>7200537</v>
+        <v>7200558</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247544</v>
+        <v>113247517</v>
       </c>
       <c r="B10" t="n">
-        <v>79222</v>
+        <v>56773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,34 +1591,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536161</v>
+        <v>536089</v>
       </c>
       <c r="R10" t="n">
-        <v>7200560</v>
+        <v>7200498</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247566</v>
+        <v>113247519</v>
       </c>
       <c r="B11" t="n">
-        <v>78158</v>
+        <v>56773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,34 +1708,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536254</v>
+        <v>536274</v>
       </c>
       <c r="R11" t="n">
-        <v>7200590</v>
+        <v>7200574</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247506</v>
+        <v>113247542</v>
       </c>
       <c r="B12" t="n">
-        <v>90765</v>
+        <v>79228</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1821,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536251</v>
+        <v>536166</v>
       </c>
       <c r="R12" t="n">
-        <v>7200583</v>
+        <v>7200538</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1894,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,7 +1924,7 @@
         <v>113247548</v>
       </c>
       <c r="B13" t="n">
-        <v>90101</v>
+        <v>90107</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247562</v>
+        <v>113247564</v>
       </c>
       <c r="B14" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536283</v>
+        <v>536273</v>
       </c>
       <c r="R14" t="n">
-        <v>7200533</v>
+        <v>7200574</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247536</v>
+        <v>113247558</v>
       </c>
       <c r="B15" t="n">
-        <v>79223</v>
+        <v>78164</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2161,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536284</v>
+        <v>536183</v>
       </c>
       <c r="R15" t="n">
-        <v>7200544</v>
+        <v>7200463</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247537</v>
+        <v>113247505</v>
       </c>
       <c r="B16" t="n">
-        <v>79223</v>
+        <v>90089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2273,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536163</v>
+        <v>536194</v>
       </c>
       <c r="R16" t="n">
-        <v>7200558</v>
+        <v>7200560</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247504</v>
+        <v>113247538</v>
       </c>
       <c r="B17" t="n">
-        <v>74339</v>
+        <v>79229</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2385,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536454</v>
+        <v>536129</v>
       </c>
       <c r="R17" t="n">
-        <v>7200443</v>
+        <v>7200562</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2481,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247528</v>
+        <v>113247561</v>
       </c>
       <c r="B18" t="n">
-        <v>56914</v>
+        <v>78164</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,38 +2497,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536056</v>
+        <v>536454</v>
       </c>
       <c r="R18" t="n">
-        <v>7200559</v>
+        <v>7200443</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247535</v>
+        <v>113247534</v>
       </c>
       <c r="B19" t="n">
-        <v>79223</v>
+        <v>79229</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536301</v>
+        <v>536166</v>
       </c>
       <c r="R19" t="n">
-        <v>7200454</v>
+        <v>7200537</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247538</v>
+        <v>113247543</v>
       </c>
       <c r="B20" t="n">
-        <v>79223</v>
+        <v>79228</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,21 +2721,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536129</v>
+        <v>536427</v>
       </c>
       <c r="R20" t="n">
-        <v>7200562</v>
+        <v>7200410</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247542</v>
+        <v>113247506</v>
       </c>
       <c r="B21" t="n">
-        <v>79222</v>
+        <v>90771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,25 +2829,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536166</v>
+        <v>536251</v>
       </c>
       <c r="R21" t="n">
-        <v>7200538</v>
+        <v>7200583</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247517</v>
+        <v>113247560</v>
       </c>
       <c r="B22" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2935,39 +2945,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536089</v>
+        <v>536312</v>
       </c>
       <c r="R22" t="n">
-        <v>7200498</v>
+        <v>7200439</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247520</v>
+        <v>113247563</v>
       </c>
       <c r="B23" t="n">
-        <v>56769</v>
+        <v>78164</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,39 +3057,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536030</v>
+        <v>536283</v>
       </c>
       <c r="R23" t="n">
-        <v>7200575</v>
+        <v>7200544</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3153,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247563</v>
+        <v>113247545</v>
       </c>
       <c r="B24" t="n">
-        <v>78158</v>
+        <v>77145</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536283</v>
+        <v>536470</v>
       </c>
       <c r="R24" t="n">
-        <v>7200544</v>
+        <v>7200485</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247503</v>
+        <v>113247567</v>
       </c>
       <c r="B25" t="n">
-        <v>77153</v>
+        <v>78164</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,21 +3281,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536467</v>
+        <v>536194</v>
       </c>
       <c r="R25" t="n">
-        <v>7200485</v>
+        <v>7200560</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247519</v>
+        <v>113247520</v>
       </c>
       <c r="B26" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536274</v>
+        <v>536030</v>
       </c>
       <c r="R26" t="n">
-        <v>7200574</v>
+        <v>7200575</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247558</v>
+        <v>113247503</v>
       </c>
       <c r="B27" t="n">
-        <v>78158</v>
+        <v>77159</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536183</v>
+        <v>536467</v>
       </c>
       <c r="R27" t="n">
-        <v>7200463</v>
+        <v>7200485</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247564</v>
+        <v>113247544</v>
       </c>
       <c r="B28" t="n">
-        <v>78158</v>
+        <v>79228</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536273</v>
+        <v>536161</v>
       </c>
       <c r="R28" t="n">
-        <v>7200574</v>
+        <v>7200560</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247566</v>
+        <v>113247505</v>
       </c>
       <c r="B2" t="n">
-        <v>78164</v>
+        <v>90089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536254</v>
+        <v>536194</v>
       </c>
       <c r="R2" t="n">
-        <v>7200590</v>
+        <v>7200560</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247528</v>
+        <v>113247543</v>
       </c>
       <c r="B3" t="n">
-        <v>56918</v>
+        <v>79228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536056</v>
+        <v>536427</v>
       </c>
       <c r="R3" t="n">
-        <v>7200559</v>
+        <v>7200410</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247535</v>
+        <v>113247562</v>
       </c>
       <c r="B4" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536301</v>
+        <v>536283</v>
       </c>
       <c r="R4" t="n">
-        <v>7200454</v>
+        <v>7200533</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247559</v>
+        <v>113247504</v>
       </c>
       <c r="B5" t="n">
-        <v>78164</v>
+        <v>74345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536304</v>
+        <v>536454</v>
       </c>
       <c r="R5" t="n">
-        <v>7200451</v>
+        <v>7200443</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247562</v>
+        <v>113247520</v>
       </c>
       <c r="B6" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,34 +1139,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536283</v>
+        <v>536030</v>
       </c>
       <c r="R6" t="n">
-        <v>7200533</v>
+        <v>7200575</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247536</v>
+        <v>113247506</v>
       </c>
       <c r="B7" t="n">
-        <v>79229</v>
+        <v>90771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536284</v>
+        <v>536251</v>
       </c>
       <c r="R7" t="n">
-        <v>7200544</v>
+        <v>7200583</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247504</v>
+        <v>113247544</v>
       </c>
       <c r="B8" t="n">
-        <v>74345</v>
+        <v>79228</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536454</v>
+        <v>536161</v>
       </c>
       <c r="R8" t="n">
-        <v>7200443</v>
+        <v>7200560</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1426,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247537</v>
+        <v>113247567</v>
       </c>
       <c r="B9" t="n">
-        <v>79229</v>
+        <v>78164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536163</v>
+        <v>536194</v>
       </c>
       <c r="R9" t="n">
-        <v>7200558</v>
+        <v>7200560</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247517</v>
+        <v>113247536</v>
       </c>
       <c r="B10" t="n">
-        <v>56773</v>
+        <v>79229</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,39 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536089</v>
+        <v>536284</v>
       </c>
       <c r="R10" t="n">
-        <v>7200498</v>
+        <v>7200544</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247519</v>
+        <v>113247560</v>
       </c>
       <c r="B11" t="n">
-        <v>56773</v>
+        <v>78164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,39 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536274</v>
+        <v>536312</v>
       </c>
       <c r="R11" t="n">
-        <v>7200574</v>
+        <v>7200439</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247542</v>
+        <v>113247535</v>
       </c>
       <c r="B12" t="n">
-        <v>79228</v>
+        <v>79229</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536166</v>
+        <v>536301</v>
       </c>
       <c r="R12" t="n">
-        <v>7200538</v>
+        <v>7200454</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1884,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247548</v>
+        <v>113247537</v>
       </c>
       <c r="B13" t="n">
-        <v>90107</v>
+        <v>79229</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536284</v>
+        <v>536163</v>
       </c>
       <c r="R13" t="n">
-        <v>7200530</v>
+        <v>7200558</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2006,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247564</v>
+        <v>113247558</v>
       </c>
       <c r="B14" t="n">
         <v>78164</v>
@@ -2073,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536273</v>
+        <v>536183</v>
       </c>
       <c r="R14" t="n">
-        <v>7200574</v>
+        <v>7200463</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247558</v>
+        <v>113247538</v>
       </c>
       <c r="B15" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,21 +2152,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536183</v>
+        <v>536129</v>
       </c>
       <c r="R15" t="n">
-        <v>7200463</v>
+        <v>7200562</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247505</v>
+        <v>113247545</v>
       </c>
       <c r="B16" t="n">
-        <v>90089</v>
+        <v>77145</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2297,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536194</v>
+        <v>536470</v>
       </c>
       <c r="R16" t="n">
-        <v>7200560</v>
+        <v>7200485</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247538</v>
+        <v>113247503</v>
       </c>
       <c r="B17" t="n">
-        <v>79229</v>
+        <v>77159</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536129</v>
+        <v>536467</v>
       </c>
       <c r="R17" t="n">
-        <v>7200562</v>
+        <v>7200485</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2593,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247534</v>
+        <v>113247517</v>
       </c>
       <c r="B19" t="n">
-        <v>79229</v>
+        <v>56773</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2609,34 +2600,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536166</v>
+        <v>536089</v>
       </c>
       <c r="R19" t="n">
-        <v>7200537</v>
+        <v>7200498</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247543</v>
+        <v>113247559</v>
       </c>
       <c r="B20" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536427</v>
+        <v>536304</v>
       </c>
       <c r="R20" t="n">
-        <v>7200410</v>
+        <v>7200451</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247506</v>
+        <v>113247542</v>
       </c>
       <c r="B21" t="n">
-        <v>90771</v>
+        <v>79228</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,25 +2825,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536251</v>
+        <v>536166</v>
       </c>
       <c r="R21" t="n">
-        <v>7200583</v>
+        <v>7200538</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247560</v>
+        <v>113247519</v>
       </c>
       <c r="B22" t="n">
-        <v>78164</v>
+        <v>56773</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,34 +2941,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536312</v>
+        <v>536274</v>
       </c>
       <c r="R22" t="n">
-        <v>7200439</v>
+        <v>7200574</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247545</v>
+        <v>113247548</v>
       </c>
       <c r="B24" t="n">
-        <v>77145</v>
+        <v>90107</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536470</v>
+        <v>536284</v>
       </c>
       <c r="R24" t="n">
-        <v>7200485</v>
+        <v>7200530</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,10 +3266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247567</v>
+        <v>113247534</v>
       </c>
       <c r="B25" t="n">
-        <v>78164</v>
+        <v>79229</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,21 +3282,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3306,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536194</v>
+        <v>536166</v>
       </c>
       <c r="R25" t="n">
-        <v>7200560</v>
+        <v>7200537</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3378,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247520</v>
+        <v>113247566</v>
       </c>
       <c r="B26" t="n">
-        <v>56773</v>
+        <v>78164</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3393,39 +3394,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536030</v>
+        <v>536254</v>
       </c>
       <c r="R26" t="n">
-        <v>7200575</v>
+        <v>7200590</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3463,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3490,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247503</v>
+        <v>113247528</v>
       </c>
       <c r="B27" t="n">
-        <v>77159</v>
+        <v>56918</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,34 +3506,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>314</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536467</v>
+        <v>536056</v>
       </c>
       <c r="R27" t="n">
-        <v>7200485</v>
+        <v>7200559</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247544</v>
+        <v>113247564</v>
       </c>
       <c r="B28" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536161</v>
+        <v>536273</v>
       </c>
       <c r="R28" t="n">
-        <v>7200560</v>
+        <v>7200574</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247505</v>
+        <v>113247537</v>
       </c>
       <c r="B2" t="n">
-        <v>90089</v>
+        <v>79236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536194</v>
+        <v>536163</v>
       </c>
       <c r="R2" t="n">
-        <v>7200560</v>
+        <v>7200558</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247543</v>
+        <v>113247506</v>
       </c>
       <c r="B3" t="n">
-        <v>79228</v>
+        <v>90778</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536427</v>
+        <v>536251</v>
       </c>
       <c r="R3" t="n">
-        <v>7200410</v>
+        <v>7200583</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247562</v>
+        <v>113247559</v>
       </c>
       <c r="B4" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536283</v>
+        <v>536304</v>
       </c>
       <c r="R4" t="n">
-        <v>7200533</v>
+        <v>7200451</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113247504</v>
+        <v>113247520</v>
       </c>
       <c r="B5" t="n">
-        <v>74345</v>
+        <v>56780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536454</v>
+        <v>536030</v>
       </c>
       <c r="R5" t="n">
-        <v>7200443</v>
+        <v>7200575</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247520</v>
+        <v>113247528</v>
       </c>
       <c r="B6" t="n">
-        <v>56773</v>
+        <v>56925</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,27 +1144,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536030</v>
+        <v>536056</v>
       </c>
       <c r="R6" t="n">
-        <v>7200575</v>
+        <v>7200559</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247506</v>
+        <v>113247548</v>
       </c>
       <c r="B7" t="n">
-        <v>90771</v>
+        <v>90114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1256,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536251</v>
+        <v>536284</v>
       </c>
       <c r="R7" t="n">
-        <v>7200583</v>
+        <v>7200530</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247544</v>
+        <v>113247562</v>
       </c>
       <c r="B8" t="n">
-        <v>79228</v>
+        <v>78171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536161</v>
+        <v>536283</v>
       </c>
       <c r="R8" t="n">
-        <v>7200560</v>
+        <v>7200533</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247567</v>
+        <v>113247544</v>
       </c>
       <c r="B9" t="n">
-        <v>78164</v>
+        <v>79235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,7 +1508,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536194</v>
+        <v>536161</v>
       </c>
       <c r="R9" t="n">
         <v>7200560</v>
@@ -1539,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247536</v>
+        <v>113247563</v>
       </c>
       <c r="B10" t="n">
-        <v>79229</v>
+        <v>78171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1596,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,7 +1620,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536284</v>
+        <v>536283</v>
       </c>
       <c r="R10" t="n">
         <v>7200544</v>
@@ -1688,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247560</v>
+        <v>113247564</v>
       </c>
       <c r="B11" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536312</v>
+        <v>536273</v>
       </c>
       <c r="R11" t="n">
-        <v>7200439</v>
+        <v>7200574</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247535</v>
+        <v>113247567</v>
       </c>
       <c r="B12" t="n">
-        <v>79229</v>
+        <v>78171</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536301</v>
+        <v>536194</v>
       </c>
       <c r="R12" t="n">
-        <v>7200454</v>
+        <v>7200560</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247537</v>
+        <v>113247505</v>
       </c>
       <c r="B13" t="n">
-        <v>79229</v>
+        <v>90096</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536163</v>
+        <v>536194</v>
       </c>
       <c r="R13" t="n">
-        <v>7200558</v>
+        <v>7200560</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247558</v>
+        <v>113247519</v>
       </c>
       <c r="B14" t="n">
-        <v>78164</v>
+        <v>56780</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,34 +2044,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536183</v>
+        <v>536274</v>
       </c>
       <c r="R14" t="n">
-        <v>7200463</v>
+        <v>7200574</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2118,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247538</v>
+        <v>113247503</v>
       </c>
       <c r="B15" t="n">
-        <v>79229</v>
+        <v>77166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,21 +2161,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2185,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536129</v>
+        <v>536467</v>
       </c>
       <c r="R15" t="n">
-        <v>7200562</v>
+        <v>7200485</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2230,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247545</v>
+        <v>113247542</v>
       </c>
       <c r="B16" t="n">
-        <v>77145</v>
+        <v>79235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2273,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536470</v>
+        <v>536166</v>
       </c>
       <c r="R16" t="n">
-        <v>7200485</v>
+        <v>7200538</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2332,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2342,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2369,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247503</v>
+        <v>113247543</v>
       </c>
       <c r="B17" t="n">
-        <v>77159</v>
+        <v>79235</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,21 +2385,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536467</v>
+        <v>536427</v>
       </c>
       <c r="R17" t="n">
-        <v>7200485</v>
+        <v>7200410</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,7 +2484,7 @@
         <v>113247561</v>
       </c>
       <c r="B18" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2584,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247517</v>
+        <v>113247558</v>
       </c>
       <c r="B19" t="n">
-        <v>56773</v>
+        <v>78171</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,39 +2609,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536089</v>
+        <v>536183</v>
       </c>
       <c r="R19" t="n">
-        <v>7200498</v>
+        <v>7200463</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247559</v>
+        <v>113247538</v>
       </c>
       <c r="B20" t="n">
-        <v>78164</v>
+        <v>79236</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,21 +2721,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536304</v>
+        <v>536129</v>
       </c>
       <c r="R20" t="n">
-        <v>7200451</v>
+        <v>7200562</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247542</v>
+        <v>113247534</v>
       </c>
       <c r="B21" t="n">
-        <v>79228</v>
+        <v>79236</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,21 +2833,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2856,7 +2860,7 @@
         <v>536166</v>
       </c>
       <c r="R21" t="n">
-        <v>7200538</v>
+        <v>7200537</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2925,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247519</v>
+        <v>113247517</v>
       </c>
       <c r="B22" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2961,7 +2965,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2970,10 +2974,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536274</v>
+        <v>536089</v>
       </c>
       <c r="R22" t="n">
-        <v>7200574</v>
+        <v>7200498</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3005,7 +3009,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3019,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113247563</v>
+        <v>113247504</v>
       </c>
       <c r="B23" t="n">
-        <v>78164</v>
+        <v>74352</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3058,21 +3062,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>536283</v>
+        <v>536454</v>
       </c>
       <c r="R23" t="n">
-        <v>7200544</v>
+        <v>7200443</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3131,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,10 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247548</v>
+        <v>113247566</v>
       </c>
       <c r="B24" t="n">
-        <v>90107</v>
+        <v>78171</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,21 +3174,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536284</v>
+        <v>536254</v>
       </c>
       <c r="R24" t="n">
-        <v>7200530</v>
+        <v>7200590</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3229,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3243,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247534</v>
+        <v>113247560</v>
       </c>
       <c r="B25" t="n">
-        <v>79229</v>
+        <v>78171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3282,21 +3286,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3306,10 +3310,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536166</v>
+        <v>536312</v>
       </c>
       <c r="R25" t="n">
-        <v>7200537</v>
+        <v>7200439</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3341,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247566</v>
+        <v>113247545</v>
       </c>
       <c r="B26" t="n">
-        <v>78164</v>
+        <v>77152</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,21 +3398,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3418,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536254</v>
+        <v>536470</v>
       </c>
       <c r="R26" t="n">
-        <v>7200590</v>
+        <v>7200485</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3453,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247528</v>
+        <v>113247536</v>
       </c>
       <c r="B27" t="n">
-        <v>56918</v>
+        <v>79236</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3506,38 +3510,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536056</v>
+        <v>536284</v>
       </c>
       <c r="R27" t="n">
-        <v>7200559</v>
+        <v>7200544</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247564</v>
+        <v>113247535</v>
       </c>
       <c r="B28" t="n">
-        <v>78164</v>
+        <v>79236</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3622,21 +3622,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536273</v>
+        <v>536301</v>
       </c>
       <c r="R28" t="n">
-        <v>7200574</v>
+        <v>7200454</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49141-2023 artfynd.xlsx
+++ b/artfynd/A 49141-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113247563</v>
+        <v>113247503</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536283</v>
+        <v>536467</v>
       </c>
       <c r="R2" t="n">
-        <v>7200544</v>
+        <v>7200485</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113247559</v>
+        <v>113247505</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536304</v>
+        <v>536194</v>
       </c>
       <c r="R3" t="n">
-        <v>7200451</v>
+        <v>7200560</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113247520</v>
+        <v>113247534</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536030</v>
+        <v>536166</v>
       </c>
       <c r="R4" t="n">
-        <v>7200575</v>
+        <v>7200537</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,12 +999,7 @@
         <v>113247535</v>
       </c>
       <c r="B5" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113247534</v>
+        <v>113247536</v>
       </c>
       <c r="B6" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536166</v>
+        <v>536284</v>
       </c>
       <c r="R6" t="n">
-        <v>7200537</v>
+        <v>7200545</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113247567</v>
+        <v>113247537</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536194</v>
+        <v>536163</v>
       </c>
       <c r="R7" t="n">
-        <v>7200560</v>
+        <v>7200558</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113247543</v>
+        <v>113247538</v>
       </c>
       <c r="B8" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>536427</v>
+        <v>536129</v>
       </c>
       <c r="R8" t="n">
-        <v>7200409</v>
+        <v>7200562</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,54 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113247528</v>
+        <v>113247506</v>
       </c>
       <c r="B9" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>536056</v>
+        <v>536251</v>
       </c>
       <c r="R9" t="n">
-        <v>7200560</v>
+        <v>7200583</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113247548</v>
+        <v>113247558</v>
       </c>
       <c r="B10" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>536284</v>
+        <v>536183</v>
       </c>
       <c r="R10" t="n">
-        <v>7200531</v>
+        <v>7200463</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,19 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113247560</v>
+        <v>113247559</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1732,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>536312</v>
+        <v>536304</v>
       </c>
       <c r="R11" t="n">
-        <v>7200439</v>
+        <v>7200451</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,19 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113247558</v>
+        <v>113247560</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1844,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>536183</v>
+        <v>536312</v>
       </c>
       <c r="R12" t="n">
-        <v>7200463</v>
+        <v>7200439</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,37 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113247544</v>
+        <v>113247561</v>
       </c>
       <c r="B13" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>536161</v>
+        <v>536454</v>
       </c>
       <c r="R13" t="n">
-        <v>7200560</v>
+        <v>7200443</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,37 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113247545</v>
+        <v>113247562</v>
       </c>
       <c r="B14" t="n">
-        <v>77450</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>536470</v>
+        <v>536283</v>
       </c>
       <c r="R14" t="n">
-        <v>7200485</v>
+        <v>7200532</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,19 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113247566</v>
+        <v>113247563</v>
       </c>
       <c r="B15" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2180,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>536254</v>
+        <v>536283</v>
       </c>
       <c r="R15" t="n">
-        <v>7200590</v>
+        <v>7200544</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,37 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113247504</v>
+        <v>113247564</v>
       </c>
       <c r="B16" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>536454</v>
+        <v>536273</v>
       </c>
       <c r="R16" t="n">
-        <v>7200443</v>
+        <v>7200574</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,37 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113247503</v>
+        <v>113247566</v>
       </c>
       <c r="B17" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>536467</v>
+        <v>536254</v>
       </c>
       <c r="R17" t="n">
-        <v>7200485</v>
+        <v>7200590</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,37 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113247536</v>
+        <v>113247567</v>
       </c>
       <c r="B18" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>536284</v>
+        <v>536194</v>
       </c>
       <c r="R18" t="n">
-        <v>7200545</v>
+        <v>7200560</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,37 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113247506</v>
+        <v>113247504</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>536251</v>
+        <v>536454</v>
       </c>
       <c r="R19" t="n">
-        <v>7200583</v>
+        <v>7200443</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,15 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113247537</v>
+        <v>113247542</v>
       </c>
       <c r="B20" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>536163</v>
+        <v>536166</v>
       </c>
       <c r="R20" t="n">
-        <v>7200558</v>
+        <v>7200537</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,15 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113247538</v>
+        <v>113247543</v>
       </c>
       <c r="B21" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>536129</v>
+        <v>536427</v>
       </c>
       <c r="R21" t="n">
-        <v>7200562</v>
+        <v>7200409</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,15 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113247542</v>
+        <v>113247544</v>
       </c>
       <c r="B22" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>536166</v>
+        <v>536161</v>
       </c>
       <c r="R22" t="n">
-        <v>7200538</v>
+        <v>7200560</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,12 +2925,7 @@
         <v>113247517</v>
       </c>
       <c r="B23" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3153,15 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113247561</v>
+        <v>113247519</v>
       </c>
       <c r="B24" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,34 +3045,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>536454</v>
+        <v>536274</v>
       </c>
       <c r="R24" t="n">
-        <v>7200443</v>
+        <v>7200574</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,15 +3146,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113247505</v>
+        <v>113247520</v>
       </c>
       <c r="B25" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,34 +3157,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>536194</v>
+        <v>536030</v>
       </c>
       <c r="R25" t="n">
-        <v>7200560</v>
+        <v>7200575</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3221,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3231,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,15 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113247564</v>
+        <v>113247521</v>
       </c>
       <c r="B26" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,34 +3269,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>536273</v>
+        <v>536008</v>
       </c>
       <c r="R26" t="n">
-        <v>7200574</v>
+        <v>7200582</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3452,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3343,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,15 +3370,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113247562</v>
+        <v>113247528</v>
       </c>
       <c r="B27" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3505,34 +3381,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536283</v>
+        <v>536056</v>
       </c>
       <c r="R27" t="n">
-        <v>7200532</v>
+        <v>7200560</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3444,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3454,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,15 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113247519</v>
+        <v>113247545</v>
       </c>
       <c r="B28" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,39 +3492,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rörtjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536274</v>
+        <v>536470</v>
       </c>
       <c r="R28" t="n">
-        <v>7200574</v>
+        <v>7200485</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3681,7 +3551,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3691,7 +3561,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
